--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="753">
   <si>
     <t>ID</t>
   </si>
@@ -1413,6 +1413,9 @@
   </si>
   <si>
     <t>2026-05-04 10:32:03.0</t>
+  </si>
+  <si>
+    <t>2026-09-22 00:00:00.0</t>
   </si>
   <si>
     <t>2221</t>
@@ -6768,7 +6771,7 @@
         <v>466</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
@@ -6779,10 +6782,10 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>8</v>
@@ -6799,10 +6802,10 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>8</v>
@@ -6819,10 +6822,10 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -6839,10 +6842,10 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -6859,10 +6862,10 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>321</v>
@@ -6879,10 +6882,10 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>409</v>
@@ -6919,10 +6922,10 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -6939,7 +6942,7 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>414</v>
@@ -6959,7 +6962,7 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>416</v>
@@ -6979,7 +6982,7 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>421</v>
@@ -6999,7 +7002,7 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>424</v>
@@ -7019,7 +7022,7 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>7</v>
@@ -7039,10 +7042,10 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -7059,16 +7062,16 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
@@ -7079,10 +7082,10 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -7099,16 +7102,16 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7119,10 +7122,10 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -7139,10 +7142,10 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>8</v>
@@ -7159,10 +7162,10 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -7179,10 +7182,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -7199,10 +7202,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -7219,10 +7222,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -7239,10 +7242,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -7259,10 +7262,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -7279,10 +7282,10 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>321</v>
@@ -7299,10 +7302,10 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -7319,10 +7322,10 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -7339,16 +7342,16 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>10</v>
@@ -7359,10 +7362,10 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -7379,16 +7382,16 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>10</v>
@@ -7399,10 +7402,10 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>321</v>
@@ -7419,10 +7422,10 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>321</v>
@@ -7439,10 +7442,10 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -7459,10 +7462,10 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -7479,10 +7482,10 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -7499,10 +7502,10 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -7519,10 +7522,10 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -7539,10 +7542,10 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -7559,13 +7562,13 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
@@ -7579,10 +7582,10 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -7599,10 +7602,10 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7619,10 +7622,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7659,10 +7662,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7679,10 +7682,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7699,10 +7702,10 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
@@ -7719,10 +7722,10 @@
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -7739,16 +7742,16 @@
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -7759,10 +7762,10 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7779,10 +7782,10 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -7799,10 +7802,10 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -7819,13 +7822,13 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7839,10 +7842,10 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>321</v>
@@ -7859,7 +7862,7 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>409</v>
@@ -7879,10 +7882,10 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -7899,7 +7902,7 @@
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>414</v>
@@ -7919,7 +7922,7 @@
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>416</v>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>421</v>
@@ -7959,7 +7962,7 @@
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>424</v>
@@ -7979,7 +7982,7 @@
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>7</v>
@@ -7999,10 +8002,10 @@
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -8019,10 +8022,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8039,10 +8042,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8059,10 +8062,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8079,10 +8082,10 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8099,10 +8102,10 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -8119,10 +8122,10 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -8139,10 +8142,10 @@
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -8159,10 +8162,10 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -8179,10 +8182,10 @@
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
@@ -8199,10 +8202,10 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>321</v>
@@ -8219,10 +8222,10 @@
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>321</v>
@@ -8239,10 +8242,10 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -8259,10 +8262,10 @@
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8279,10 +8282,10 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -8299,10 +8302,10 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -8319,10 +8322,10 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -8339,10 +8342,10 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -8359,10 +8362,10 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>321</v>
@@ -8379,10 +8382,10 @@
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>339</v>
@@ -8399,13 +8402,13 @@
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>9</v>
@@ -8419,10 +8422,10 @@
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8439,7 +8442,7 @@
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>409</v>
@@ -8459,10 +8462,10 @@
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -8479,7 +8482,7 @@
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>414</v>
@@ -8499,7 +8502,7 @@
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>416</v>
@@ -8519,7 +8522,7 @@
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>421</v>
@@ -8539,7 +8542,7 @@
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>424</v>
@@ -8559,10 +8562,10 @@
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>354</v>
@@ -8579,10 +8582,10 @@
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>321</v>
@@ -8599,7 +8602,7 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>7</v>
@@ -8619,10 +8622,10 @@
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -8639,10 +8642,10 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -8659,10 +8662,10 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -8679,10 +8682,10 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -8699,10 +8702,10 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -8719,10 +8722,10 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>8</v>
@@ -8739,10 +8742,10 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>8</v>
@@ -8759,10 +8762,10 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -8779,10 +8782,10 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>321</v>
@@ -8799,10 +8802,10 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>321</v>
@@ -8819,10 +8822,10 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -8839,10 +8842,10 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -8859,10 +8862,10 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -8879,10 +8882,10 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -8899,10 +8902,10 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -8919,10 +8922,10 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>8</v>
@@ -8939,10 +8942,10 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -8959,10 +8962,10 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -8979,10 +8982,10 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>321</v>
@@ -8999,10 +9002,10 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -9019,10 +9022,10 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>8</v>
@@ -9039,10 +9042,10 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -9059,10 +9062,10 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -9079,10 +9082,10 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>304</v>
@@ -9099,10 +9102,10 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -9119,10 +9122,10 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -9139,10 +9142,10 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -9159,10 +9162,10 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>8</v>
@@ -9179,10 +9182,10 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -9199,10 +9202,10 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -9219,10 +9222,10 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>304</v>
@@ -9239,10 +9242,10 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C346" s="2" t="s">
         <v>8</v>
@@ -9259,10 +9262,10 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C347" s="2" t="s">
         <v>8</v>
@@ -9279,10 +9282,10 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>339</v>
@@ -9299,10 +9302,10 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>321</v>
@@ -9319,10 +9322,10 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>304</v>
@@ -9339,13 +9342,13 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
@@ -9359,10 +9362,10 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -9379,10 +9382,10 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -9399,10 +9402,10 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -9419,10 +9422,10 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -9439,10 +9442,10 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -9459,10 +9462,10 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -9479,10 +9482,10 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -9499,10 +9502,10 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -9519,10 +9522,10 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -9539,10 +9542,10 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -9559,10 +9562,10 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -9579,10 +9582,10 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>8</v>
@@ -9599,10 +9602,10 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -9619,10 +9622,10 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>8</v>
@@ -9639,10 +9642,10 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>8</v>
@@ -9659,10 +9662,10 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>304</v>
@@ -9679,10 +9682,10 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -9699,10 +9702,10 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>304</v>
@@ -9719,10 +9722,10 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>304</v>
@@ -9739,10 +9742,10 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>403</v>
@@ -9759,10 +9762,10 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -9779,7 +9782,7 @@
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>409</v>
@@ -9799,10 +9802,10 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>8</v>
@@ -9819,7 +9822,7 @@
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>414</v>
@@ -9839,7 +9842,7 @@
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>416</v>
@@ -9859,7 +9862,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>421</v>
@@ -9879,7 +9882,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>424</v>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -1082,7 +1082,7 @@
     <t>1333</t>
   </si>
   <si>
-    <t>Trascrizione decreto prefettizio cambio cognome multi intestatari</t>
+    <t>Trascrizione provvedimento cambio cognome multi intestatari da Prefettura o Tribunale</t>
   </si>
   <si>
     <t>1334</t>
